--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-26.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_2B59D187542A3A6CE3BA301159E338F74939EDA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4E3B1FC-977E-4304-AD33-7AE3F4121004}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_2B59D187542A3A6CE3BA301159E338F74939EDA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B14E297F-34B8-463F-8E79-237BBB270B7E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="48">
   <si>
     <t>Data</t>
   </si>
@@ -171,15 +171,6 @@
   </si>
   <si>
     <t>River Plate x Santa Fe</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>COLOMBIA 1</t>
-  </si>
-  <si>
-    <t>Atletico Nacional Medellin x Deportivo Cali</t>
   </si>
   <si>
     <t>1/0</t>
@@ -566,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="19.33203125" customWidth="1"/>
@@ -607,10 +598,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -693,7 +684,7 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M14" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
+        <f t="shared" ref="M3:M13" si="0">IF(L3=1,0.965/(H3-1),-1)</f>
         <v>0.15031152647975077</v>
       </c>
     </row>
@@ -1115,48 +1106,6 @@
       <c r="M13">
         <f t="shared" si="0"/>
         <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14">
-        <v>13.12</v>
-      </c>
-      <c r="I14">
-        <v>1.6</v>
-      </c>
-      <c r="J14" t="s">
-        <v>18</v>
-      </c>
-      <c r="K14" t="s">
-        <v>19</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>7.9620462046204626E-2</v>
       </c>
     </row>
   </sheetData>
